--- a/data/trans_orig/POLIPATOLOGIA_Lim_2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_2-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2012</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40059</t>
+          <t>39320</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68851</t>
+          <t>68362</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27239</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52017</t>
+          <t>51564</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72290</t>
+          <t>72902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111179</t>
+          <t>108866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>368360</t>
+          <t>368849</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397152</t>
+          <t>397891</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>262437</t>
+          <t>262890</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287215</t>
+          <t>287811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>640486</t>
+          <t>642799</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>679375</t>
+          <t>678763</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,3%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42961</t>
+          <t>41158</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73658</t>
+          <t>72248</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50734</t>
+          <t>49228</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80616</t>
+          <t>79831</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99707</t>
+          <t>99498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143211</t>
+          <t>143003</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>345139</t>
+          <t>346549</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375836</t>
+          <t>377639</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>257395</t>
+          <t>258180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>287277</t>
+          <t>288783</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>613597</t>
+          <t>613805</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>657101</t>
+          <t>657310</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>119842</t>
+          <t>120794</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>165294</t>
+          <t>162415</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60533</t>
+          <t>60707</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90808</t>
+          <t>90994</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>191211</t>
+          <t>185668</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>244992</t>
+          <t>242533</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>464121</t>
+          <t>467000</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>509573</t>
+          <t>508621</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169321</t>
+          <t>169135</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>199596</t>
+          <t>199422</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644552</t>
+          <t>647011</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>698333</t>
+          <t>703876</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>202727</t>
+          <t>201102</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>260073</t>
+          <t>258495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>138044</t>
+          <t>136464</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>185396</t>
+          <t>182884</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>349224</t>
+          <t>352140</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>425029</t>
+          <t>427048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>898936</t>
+          <t>900514</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>956282</t>
+          <t>957907</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>581261</t>
+          <t>583773</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>628613</t>
+          <t>630193</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1500638</t>
+          <t>1498619</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1576443</t>
+          <t>1573527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,71%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77847</t>
+          <t>78923</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112096</t>
+          <t>112745</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>253045</t>
+          <t>256399</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>309143</t>
+          <t>307640</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>342418</t>
+          <t>343847</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>407647</t>
+          <t>412687</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>398500</t>
+          <t>397851</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>432749</t>
+          <t>431673</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>452379</t>
+          <t>453882</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>508477</t>
+          <t>505123</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>864471</t>
+          <t>859431</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>929700</t>
+          <t>928271</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,97%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>18717</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>386413</t>
+          <t>386539</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>451880</t>
+          <t>452488</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>393833</t>
+          <t>391107</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>465647</t>
+          <t>464124</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249520</t>
+          <t>248165</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263798</t>
+          <t>263762</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>657471</t>
+          <t>656863</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>722938</t>
+          <t>722812</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>910586</t>
+          <t>912109</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>982400</t>
+          <t>985126</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,58%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>534346</t>
+          <t>534943</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>628361</t>
+          <t>622457</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>981902</t>
+          <t>981486</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1088258</t>
+          <t>1094456</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1540170</t>
+          <t>1540667</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1686798</t>
+          <t>1679235</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2793549</t>
+          <t>2799453</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2887564</t>
+          <t>2886967</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2461867</t>
+          <t>2455669</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2568223</t>
+          <t>2568639</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5285237</t>
+          <t>5292800</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5431865</t>
+          <t>5431368</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,9%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2016</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40137</t>
+          <t>39675</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68942</t>
+          <t>68297</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35248</t>
+          <t>34317</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61790</t>
+          <t>62537</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82288</t>
+          <t>82173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121722</t>
+          <t>121192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>360150</t>
+          <t>360795</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>388955</t>
+          <t>389417</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285265</t>
+          <t>284518</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311807</t>
+          <t>312738</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>654425</t>
+          <t>654955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>693859</t>
+          <t>693974</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,41%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33356</t>
+          <t>32455</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59676</t>
+          <t>58235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40449</t>
+          <t>41539</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69992</t>
+          <t>69756</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80384</t>
+          <t>80513</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117958</t>
+          <t>119854</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>317551</t>
+          <t>318992</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>343871</t>
+          <t>344772</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>302281</t>
+          <t>302517</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>331824</t>
+          <t>330734</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>631542</t>
+          <t>629646</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>669116</t>
+          <t>668987</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,26%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69545</t>
+          <t>68160</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100510</t>
+          <t>101561</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39607</t>
+          <t>41079</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65695</t>
+          <t>66266</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116274</t>
+          <t>117258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159682</t>
+          <t>161189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>421404</t>
+          <t>420353</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452369</t>
+          <t>453754</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100428</t>
+          <t>99857</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>126516</t>
+          <t>125044</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>528354</t>
+          <t>526847</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>571762</t>
+          <t>570778</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,96%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>167055</t>
+          <t>166651</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>215466</t>
+          <t>216250</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>137913</t>
+          <t>138198</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>185119</t>
+          <t>185134</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>318637</t>
+          <t>317271</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>384562</t>
+          <t>385326</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>934172</t>
+          <t>933388</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>982583</t>
+          <t>982987</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>640757</t>
+          <t>640742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>687963</t>
+          <t>687678</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1590952</t>
+          <t>1590188</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1656877</t>
+          <t>1658243</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,94%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107724</t>
+          <t>107115</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147399</t>
+          <t>145046</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>224507</t>
+          <t>224322</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>277568</t>
+          <t>277867</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>344860</t>
+          <t>343352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>411761</t>
+          <t>409663</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>473307</t>
+          <t>475660</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>512982</t>
+          <t>513591</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>460676</t>
+          <t>460377</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>513737</t>
+          <t>513922</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>947189</t>
+          <t>949287</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1014090</t>
+          <t>1015598</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,73%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14913</t>
+          <t>15860</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>305575</t>
+          <t>304763</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>370261</t>
+          <t>370353</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>313586</t>
+          <t>312072</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>380894</t>
+          <t>380024</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>272232</t>
+          <t>271285</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283232</t>
+          <t>283298</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>711764</t>
+          <t>711672</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>776450</t>
+          <t>777262</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>988276</t>
+          <t>989146</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1055584</t>
+          <t>1057098</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,21%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>466936</t>
+          <t>463019</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>550393</t>
+          <t>546206</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>852059</t>
+          <t>846782</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>961894</t>
+          <t>957768</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1347455</t>
+          <t>1343435</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1486860</t>
+          <t>1483467</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2835329</t>
+          <t>2839516</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2918786</t>
+          <t>2922703</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2569702</t>
+          <t>2573828</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2679537</t>
+          <t>2684814</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5430458</t>
+          <t>5433851</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5569863</t>
+          <t>5573883</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,58%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2023</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52374</t>
+          <t>52061</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82941</t>
+          <t>80944</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90813</t>
+          <t>90423</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>120587</t>
+          <t>120216</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>150331</t>
+          <t>151096</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>193438</t>
+          <t>191472</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422271</t>
+          <t>424268</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452838</t>
+          <t>453151</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>326880</t>
+          <t>327251</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>356654</t>
+          <t>357044</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>759241</t>
+          <t>761207</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>802348</t>
+          <t>801583</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,14%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55262</t>
+          <t>55730</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83490</t>
+          <t>85479</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88282</t>
+          <t>89124</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116762</t>
+          <t>117118</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152192</t>
+          <t>151358</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>194677</t>
+          <t>192937</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368723</t>
+          <t>366734</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>396951</t>
+          <t>396483</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>265818</t>
+          <t>265462</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>294298</t>
+          <t>293456</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>640116</t>
+          <t>641856</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>682601</t>
+          <t>683435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,87%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29447</t>
+          <t>30223</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134254</t>
+          <t>134258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56076</t>
+          <t>55575</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77241</t>
+          <t>76286</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63146</t>
+          <t>69657</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215422</t>
+          <t>212441</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534010</t>
+          <t>534006</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>638817</t>
+          <t>638041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89670</t>
+          <t>90625</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110835</t>
+          <t>111336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>619753</t>
+          <t>622734</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>772029</t>
+          <t>765518</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>206964</t>
+          <t>202900</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>261505</t>
+          <t>254696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113357</t>
+          <t>125087</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>289833</t>
+          <t>288952</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>322296</t>
+          <t>308550</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>515032</t>
+          <t>511873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>773314</t>
+          <t>780123</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>827855</t>
+          <t>831919</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>688261</t>
+          <t>689142</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>864737</t>
+          <t>853007</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1497880</t>
+          <t>1501039</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1690616</t>
+          <t>1704362</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95895</t>
+          <t>94841</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133776</t>
+          <t>132261</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>219040</t>
+          <t>235666</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>350300</t>
+          <t>355109</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>348098</t>
+          <t>344205</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>463818</t>
+          <t>461105</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,03%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>341270</t>
+          <t>342785</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>379151</t>
+          <t>380205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>491035</t>
+          <t>486226</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>622295</t>
+          <t>605669</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>852563</t>
+          <t>855276</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>968283</t>
+          <t>972176</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,85%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>12833</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44187</t>
+          <t>41194</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>251996</t>
+          <t>254984</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>300205</t>
+          <t>302068</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>270406</t>
+          <t>272284</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>327369</t>
+          <t>332782</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>196320</t>
+          <t>199313</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>227785</t>
+          <t>227674</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>461166</t>
+          <t>459303</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>509375</t>
+          <t>506387</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>674509</t>
+          <t>669096</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>731472</t>
+          <t>729594</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,82%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>441164</t>
+          <t>457994</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>647362</t>
+          <t>649457</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>863664</t>
+          <t>870021</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1169995</t>
+          <t>1167687</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1446583</t>
+          <t>1453470</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1794941</t>
+          <t>1780080</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2728698</t>
+          <t>2726603</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2934896</t>
+          <t>2918066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2407763</t>
+          <t>2410071</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2714094</t>
+          <t>2707737</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5158877</t>
+          <t>5173738</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5507235</t>
+          <t>5500348</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_Lim_2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_2-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39320</t>
+          <t>38754</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68362</t>
+          <t>67749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>26637</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51564</t>
+          <t>50738</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72902</t>
+          <t>72768</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108866</t>
+          <t>109122</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>368849</t>
+          <t>369462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397891</t>
+          <t>398457</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>262890</t>
+          <t>263716</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287811</t>
+          <t>287817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>642799</t>
+          <t>642543</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>678763</t>
+          <t>678897</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,32%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41158</t>
+          <t>42398</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72248</t>
+          <t>74451</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49228</t>
+          <t>50816</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79831</t>
+          <t>80786</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99498</t>
+          <t>98477</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143003</t>
+          <t>143782</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346549</t>
+          <t>344346</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>377639</t>
+          <t>376399</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>258180</t>
+          <t>257225</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>288783</t>
+          <t>287195</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>613805</t>
+          <t>613026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>657310</t>
+          <t>658331</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,99%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>120794</t>
+          <t>120663</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162415</t>
+          <t>165255</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60707</t>
+          <t>60884</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90994</t>
+          <t>91067</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>185668</t>
+          <t>190189</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>242533</t>
+          <t>243000</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>467000</t>
+          <t>464160</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>508621</t>
+          <t>508752</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169135</t>
+          <t>169062</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>199422</t>
+          <t>199245</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>647011</t>
+          <t>646544</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>703876</t>
+          <t>699355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>201102</t>
+          <t>200981</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>258495</t>
+          <t>256411</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>136464</t>
+          <t>138534</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182884</t>
+          <t>184037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>352140</t>
+          <t>353184</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>427048</t>
+          <t>426599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>900514</t>
+          <t>902598</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>957907</t>
+          <t>958028</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>583773</t>
+          <t>582620</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>630193</t>
+          <t>628123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1498619</t>
+          <t>1499068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1573527</t>
+          <t>1572483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,66%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78923</t>
+          <t>75758</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112745</t>
+          <t>111802</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>256399</t>
+          <t>253604</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>307640</t>
+          <t>308026</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>343847</t>
+          <t>344757</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>412687</t>
+          <t>409609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>397851</t>
+          <t>398794</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>431673</t>
+          <t>434838</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>453882</t>
+          <t>453496</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>505123</t>
+          <t>507918</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>859431</t>
+          <t>862509</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>928271</t>
+          <t>927361</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,9%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18717</t>
+          <t>17354</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>386539</t>
+          <t>385950</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>452488</t>
+          <t>453143</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>391107</t>
+          <t>389122</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>464124</t>
+          <t>461439</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248165</t>
+          <t>249528</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263762</t>
+          <t>263833</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>656863</t>
+          <t>656208</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>722812</t>
+          <t>723401</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>912109</t>
+          <t>914794</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>985126</t>
+          <t>987111</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>534943</t>
+          <t>536318</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>622457</t>
+          <t>626756</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>981486</t>
+          <t>981920</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1094456</t>
+          <t>1094401</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1540667</t>
+          <t>1553592</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1679235</t>
+          <t>1693010</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2799453</t>
+          <t>2795154</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2886967</t>
+          <t>2885592</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2455669</t>
+          <t>2455724</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2568639</t>
+          <t>2568205</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5292800</t>
+          <t>5279025</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5431368</t>
+          <t>5418443</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39675</t>
+          <t>38328</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68297</t>
+          <t>66783</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34317</t>
+          <t>34410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62537</t>
+          <t>61658</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82173</t>
+          <t>81475</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121192</t>
+          <t>119910</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>360795</t>
+          <t>362309</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>389417</t>
+          <t>390764</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>284518</t>
+          <t>285397</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312738</t>
+          <t>312645</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>654955</t>
+          <t>656237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>693974</t>
+          <t>694672</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,5%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32455</t>
+          <t>33015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58235</t>
+          <t>59586</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41539</t>
+          <t>41151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69756</t>
+          <t>70266</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80513</t>
+          <t>80600</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119854</t>
+          <t>118536</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>318992</t>
+          <t>317641</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>344772</t>
+          <t>344212</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>302517</t>
+          <t>302007</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>330734</t>
+          <t>331122</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>629646</t>
+          <t>630964</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>668987</t>
+          <t>668900</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,25%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68160</t>
+          <t>67969</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101561</t>
+          <t>102022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41079</t>
+          <t>40649</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66266</t>
+          <t>66721</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117258</t>
+          <t>114718</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161189</t>
+          <t>159474</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>420353</t>
+          <t>419892</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>453754</t>
+          <t>453945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>99857</t>
+          <t>99402</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125044</t>
+          <t>125474</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>526847</t>
+          <t>528562</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>570778</t>
+          <t>573318</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,33%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>166651</t>
+          <t>165781</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>216250</t>
+          <t>218135</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>138198</t>
+          <t>140611</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>185134</t>
+          <t>188226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>317271</t>
+          <t>317919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>385326</t>
+          <t>388163</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>933388</t>
+          <t>931503</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>982987</t>
+          <t>983857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>640742</t>
+          <t>637650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>687678</t>
+          <t>685265</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1590188</t>
+          <t>1587351</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1658243</t>
+          <t>1657595</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,91%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107115</t>
+          <t>107199</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>145046</t>
+          <t>146923</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>224322</t>
+          <t>225008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>277867</t>
+          <t>278018</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>343352</t>
+          <t>342148</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>409663</t>
+          <t>411141</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>475660</t>
+          <t>473783</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>513591</t>
+          <t>513507</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>460377</t>
+          <t>460226</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>513922</t>
+          <t>513236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>949287</t>
+          <t>947809</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1015598</t>
+          <t>1016802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,82%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15860</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>304763</t>
+          <t>307612</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>370353</t>
+          <t>369190</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>312072</t>
+          <t>313585</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>380024</t>
+          <t>381387</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271285</t>
+          <t>271715</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283298</t>
+          <t>283186</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>711672</t>
+          <t>712835</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>777262</t>
+          <t>774413</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>989146</t>
+          <t>987783</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1057098</t>
+          <t>1055585</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,1%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>463019</t>
+          <t>462062</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>546206</t>
+          <t>546704</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>846782</t>
+          <t>849497</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>957768</t>
+          <t>960735</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1343435</t>
+          <t>1345792</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1483467</t>
+          <t>1484032</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2839516</t>
+          <t>2839018</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2922703</t>
+          <t>2923660</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2573828</t>
+          <t>2570861</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2684814</t>
+          <t>2682099</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5433851</t>
+          <t>5433286</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5573883</t>
+          <t>5571526</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,54%</t>
         </is>
       </c>
     </row>
@@ -5997,32 +5997,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>66359</t>
+          <t>73878</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52061</t>
+          <t>59697</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80944</t>
+          <t>90321</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6032,32 +6032,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>104487</t>
+          <t>114492</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90423</t>
+          <t>98837</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>120216</t>
+          <t>129819</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,32 +6067,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>170846</t>
+          <t>188370</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>151096</t>
+          <t>165269</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191472</t>
+          <t>212506</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -6110,32 +6110,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>438853</t>
+          <t>476740</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>424268</t>
+          <t>460297</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453151</t>
+          <t>490921</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6145,32 +6145,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>342980</t>
+          <t>373919</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>327251</t>
+          <t>358592</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>357044</t>
+          <t>389574</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,32 +6180,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>781833</t>
+          <t>850659</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>761207</t>
+          <t>826523</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>801583</t>
+          <t>873760</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,09%</t>
         </is>
       </c>
     </row>
@@ -6223,17 +6223,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6340,32 +6340,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69547</t>
+          <t>71967</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55730</t>
+          <t>57889</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85479</t>
+          <t>86774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6375,32 +6375,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>102667</t>
+          <t>116605</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89124</t>
+          <t>103059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>117118</t>
+          <t>132020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172214</t>
+          <t>188571</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>151358</t>
+          <t>165609</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>192937</t>
+          <t>213446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>382666</t>
+          <t>411245</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366734</t>
+          <t>396438</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>396483</t>
+          <t>425323</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6488,32 +6488,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>279913</t>
+          <t>306538</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>265462</t>
+          <t>291123</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>293456</t>
+          <t>320084</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>662579</t>
+          <t>717784</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>641856</t>
+          <t>692909</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>683435</t>
+          <t>740746</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6683,32 +6683,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>80312</t>
+          <t>85708</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30223</t>
+          <t>69972</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134258</t>
+          <t>101714</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6718,32 +6718,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>65829</t>
+          <t>72605</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55575</t>
+          <t>62362</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76286</t>
+          <t>85296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>146141</t>
+          <t>158313</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69657</t>
+          <t>140023</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212441</t>
+          <t>179994</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -6796,32 +6796,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>587952</t>
+          <t>385904</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534006</t>
+          <t>369898</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>638041</t>
+          <t>401640</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6831,32 +6831,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>101082</t>
+          <t>114892</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90625</t>
+          <t>102201</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111336</t>
+          <t>125135</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>689034</t>
+          <t>500796</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622734</t>
+          <t>479115</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>765518</t>
+          <t>519086</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>78,76%</t>
         </is>
       </c>
     </row>
@@ -6909,17 +6909,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6944,17 +6944,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7026,32 +7026,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>230186</t>
+          <t>249865</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>202900</t>
+          <t>222430</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>254696</t>
+          <t>280802</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7061,32 +7061,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>221085</t>
+          <t>249032</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>125087</t>
+          <t>227725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>288952</t>
+          <t>271294</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>451271</t>
+          <t>498897</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>308550</t>
+          <t>462653</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>511873</t>
+          <t>531216</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -7139,32 +7139,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>804633</t>
+          <t>881978</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>780123</t>
+          <t>851041</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>831919</t>
+          <t>909413</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7174,32 +7174,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>757009</t>
+          <t>612179</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>689142</t>
+          <t>589917</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>853007</t>
+          <t>633486</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1561641</t>
+          <t>1494157</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1501039</t>
+          <t>1461838</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1704362</t>
+          <t>1530401</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>76,79%</t>
         </is>
       </c>
     </row>
@@ -7252,17 +7252,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7287,17 +7287,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7369,32 +7369,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>113103</t>
+          <t>121924</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94841</t>
+          <t>102401</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132261</t>
+          <t>142401</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7404,32 +7404,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>306160</t>
+          <t>330419</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>235666</t>
+          <t>308093</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>355109</t>
+          <t>355258</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>419263</t>
+          <t>452343</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>344205</t>
+          <t>421261</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>461105</t>
+          <t>484351</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,63%</t>
         </is>
       </c>
     </row>
@@ -7482,32 +7482,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>361943</t>
+          <t>446040</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>342785</t>
+          <t>425563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>380205</t>
+          <t>465563</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7517,32 +7517,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>535175</t>
+          <t>500431</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>486226</t>
+          <t>475592</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>605669</t>
+          <t>522757</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>897118</t>
+          <t>946471</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>855276</t>
+          <t>914463</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>972176</t>
+          <t>977553</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>69,88%</t>
         </is>
       </c>
     </row>
@@ -7595,17 +7595,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7712,32 +7712,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23504</t>
+          <t>23268</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12833</t>
+          <t>13477</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41194</t>
+          <t>42935</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7747,32 +7747,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>276317</t>
+          <t>301311</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>254984</t>
+          <t>275179</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>302068</t>
+          <t>329383</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>299820</t>
+          <t>324579</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>272284</t>
+          <t>294025</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>332782</t>
+          <t>354380</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -7825,32 +7825,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>217003</t>
+          <t>213960</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>199313</t>
+          <t>194293</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>227674</t>
+          <t>223751</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7860,32 +7860,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>485054</t>
+          <t>542970</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>459303</t>
+          <t>514898</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>506387</t>
+          <t>569102</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>702058</t>
+          <t>756930</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>669096</t>
+          <t>727129</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>729594</t>
+          <t>787484</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,81%</t>
         </is>
       </c>
     </row>
@@ -7938,17 +7938,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>583011</t>
+          <t>626610</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>457994</t>
+          <t>582104</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>649457</t>
+          <t>676260</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8090,32 +8090,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1076544</t>
+          <t>1184464</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>870021</t>
+          <t>1134623</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1167687</t>
+          <t>1231469</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1659555</t>
+          <t>1811074</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1453470</t>
+          <t>1745243</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1780080</t>
+          <t>1878886</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -8168,32 +8168,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2793049</t>
+          <t>2815866</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2726603</t>
+          <t>2766216</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2918066</t>
+          <t>2860372</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8203,32 +8203,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2501214</t>
+          <t>2450929</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2410071</t>
+          <t>2403924</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2707737</t>
+          <t>2500770</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5294263</t>
+          <t>5266795</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5173738</t>
+          <t>5198983</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5500348</t>
+          <t>5332626</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -8281,17 +8281,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
